--- a/reports/citeguard_results_2026-08-02.xlsx
+++ b/reports/citeguard_results_2026-08-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,179 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-02T17:27:48.723710</t>
+          <t>2026-08-02T17:47:23.798260</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is a PromptTemplate in LangChain?</t>
+          <t>How do I build a multi-agent system with LangGraph?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A PromptTemplate in LangChain is a reusable prompt template that contains placeholders (input variables) to be filled when generating prompts. You typically create one with PromptTemplate.fromTemplate by giving a template string with variable placeholders (e.g., {question}). Missing or invalid input variables (or unescaped braces in embedded JSON) can trigger an INVALID_PROMPT_INPUT error.</t>
+          <t>The provided docs do not include a step‑by‑step tutorial specifically for multi‑agent systems. However, based on the LangGraph concepts in the context, you can approach a multi‑agent system like this:
+- Model each agent as part of the graph—either as its own subgraph or as a set of nodes that implement that agent’s behavior.
+- Break each agent’s behavior into discrete nodes (steps). For each node, describe the decisions and transitions it can make.
+- Use a shared state that nodes can read from and write to to coordinate between agents (this is the primary mechanism for connecting nodes and passing information).
+- Mix deterministic, hand‑coded nodes and LLM‑driven (agentic) nodes in the same graph to get precise orchestration and behavior you control.
+- Before implementing, familiarize yourself with the underlying components LangGraph coordinates (models and tools), since LangGraph is a low‑level orchestration framework.
+If you need a concrete example or code patterns for multi‑agent coordination, the provided context doesn’t include one — I can look up or draft an example if you want.</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Several claims go beyond what the provided sources directly state:
+- Unsupported: "Model each agent as its own subgraph" — the docs describe nodes and connecting nodes via state but do not mention or document "subgraphs" as a recommended pattern in the excerpts given.
+- Partially unsupported: "Coordinate between agents using a shared state (primary mechanism)" — the docs do state that nodes are connected through a shared state that nodes can read/write, but they do not explicitly discuss multi‑agent coordination or label shared state as the primary mechanism for coordinating multiple agents.
+- Minor/implicit claim: "The provided docs do not include a step‑by‑step tutorial specifically for multi‑agent systems" — the excerpts do not contain a multi‑agent tutorial, but this absence is an inference rather than an explicit statement in the sources.
+Supported claims include breaking behavior into discrete nodes, describing decisions/transitions for nodes, mixing deterministic and LLM‑driven steps in the same graph, and the recommendation to familiarize yourself with models and tools because LangGraph is a low‑level orchestration framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:47:53.337786</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>How do I create a ChromaDB retriever?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The provided context does not include any ChromaDB-specific instructions or configuration, so I can't give ChromaDB‑specific steps.
+Based on the examples in the context, the general pattern shown is:
+- Index your (preprocessed) documents into a vector store for semantic search.
+- Use embeddings (the example uses OpenAI embeddings) when indexing.
+- Create a retriever tool from the vector store. Two examples in the docs:
+  - Wrap the vector store's similarity_search in a @chain function to make a retriever:
+    retriever(query: str) -&gt; List[Document]: return vector_store.similarity_search(query, k=1)
+  - Use LangChain/LangGraph helper (createRetrieverTool) to build a retriever tool from the vector store.
+- Test the retriever tool.
+If you want ChromaDB-specific code, the context doesn't contain it — consult the ChromaDB integration docs or the VectorStore integration docs referenced in the sources.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>The sources describe prompts as reusable prompt templates (mcp.mdx), show PromptTemplate.fromTemplate usage with variable placeholders like {question} (INVALID_PROMPT_INPUT examples), and state INVALID_PROMPT_INPUT occurs for missing/invalid input variables and when unescaped curly braces in embedded JSON are misinterpreted—so all claims are supported.</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>All claims match the provided sources: the docs state there are no ChromaDB-specific instructions; they show the general pattern of indexing preprocessed documents into a vector store, using OpenAI embeddings in the example, creating a retriever (both via wrapping vector_store.similarity_search with a @chain and via a createRetrieverTool helper), and testing the retriever. The suggestion to consult Chroma/VectorStore integration docs is consistent with the referenced "Integration-specific docs" and VectorStore API links. No unsupported claims were found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:27.237569</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>What is the difference between LangChain and LangGraph?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>- Level: LangChain provides higher-level building blocks and prebuilt agent architectures (easy starting point, “batteries‑included” options like Deep Agents). LangGraph is a low‑level orchestration framework and runtime for building, managing, and deploying long‑running, stateful agents.
+- Control vs. convenience: LangChain favors convenience and ready‑made agent patterns; LangGraph gives fine‑grained control and low‑level flexibility for custom orchestration.
+- Capabilities: LangGraph emphasizes durable execution, streaming, human‑in‑the‑loop, and mixing deterministic (hand‑coded) steps with LLM‑driven steps in a single graph. LangChain is commonly used to integrate models and tools and to provide higher‑level agent abstractions.
+- Interoperability: You can use LangChain components with LangGraph, but LangGraph does not require LangChain. LangGraph also provides one high‑level agent abstraction compatible with LangChain’s ReAct interface.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Each point in the generated answer is supported by the provided sources: LangChain is described as higher-level with prebuilt agents (including "Deep Agents" as a batteries‑included option) and is commonly used to integrate models/tools; LangGraph is described as a low‑level orchestration framework/runtime for long‑running, stateful agents that provides fine‑grained control, durable execution, streaming, human‑in‑the‑loop capabilities, and the ability to mix deterministic and LLM-driven steps. The sources also state you can use LangChain components with LangGraph but don't have to, and that LangGraph exposes one high‑level agent abstraction with the same ReAct-compatible interface. No unsupported claims were found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:49:00.794139</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>What is a StateGraph in LangGraph?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>StateGraph is the LangGraph class you use to define a graph that operates on a given State (the shared state/schema). You instantiate it with your State, then add nodes and edges (e.g., .addNode, .addEdge) and call .compile() to produce the graph.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The sources explicitly show importing StateGraph and using it with a State (new StateGraph(State)), calling .addNode and .addEdge, and then .compile(); the use-graph-api text likewise states StateGraph is used "to define a graph that operates on this state." All claims in the answer are supported by the provided excerpts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:49:29.267220</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>What is human-in-the-loop in LangGraph?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Human-in-the-loop in LangGraph is middleware that adds human oversight to agent tool calls: when a model proposes an action that might need review (e.g., writing a file or running SQL), the middleware checks the call against a configurable policy and—if intervention is required—issues an interrupt that pauses execution. The graph state is saved via LangGraph’s persistence layer so execution can be safely resumed, and a human decision drives the next step (approve, edit, reject, or respond).</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Each claim in the generated answer is directly supported by the provided sources: the Human-in-the-Loop is described as middleware that adds human oversight to agent tool calls; it pauses execution for actions needing review (examples: writing a file, executing SQL); it checks tool calls against a configurable policy and issues an interrupt to halt execution; the graph state is saved using LangGraph's persistence layer so execution can resume; and the human decision options are approve, edit, reject, or respond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:50:02.522751</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>How do I add memory to a LangGraph agent?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>There are two kinds of memory in LangGraph:
+- Short-term memory (thread-level persistence) — use it for multi-turn conversations. Example (Python):
+  - from langgraph.checkpoint.memory import InMemorySaver
+  - checkpointer = InMemorySaver()
+  - builder = StateGraph(...)
+  - graph = builder.compile(checkpointer=checkpointer)
+  (JS equivalent: import { MemorySaver } from "@langchain/langgraph"; const checkpointer = new MemorySaver();)
+- Long-term memory (persists across threads/sessions) — built on LangGraph stores (JSON docs by namespace/key). To add it, create a store (e.g., InMemoryStore or a PostgreSQL-backed store) and pass that store to create_agent. For PostgreSQL you can install the checkpoint package (pip install langgraph-checkpoint-postgres).</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Each claim matches the source documents: the docs state there are two memory types; short-term memory is thread-level persistence for multi-turn conversations and show the Python example (from langgraph.checkpoint.memory import InMemorySaver; checkpointer = InMemorySaver(); builder = StateGraph(...); graph = builder.compile(checkpointer=checkpointer)); the Quickstart JS snippet shows import { MemorySaver } from "@langchain/langgraph" and new MemorySaver(); long-term memory is described as persisting across threads/sessions, built on LangGraph stores (JSON documents by namespace/key), and the docs show creating a store (InMemoryStore or PostgreSQL) and passing it to create_agent, including the pip install langgraph-checkpoint-postgres example. All claims are supported.</t>
         </is>
       </c>
     </row>
